--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Desktop\general\monthly-report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Waltana\Desktop from C\general\monthly-report\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>business_date</t>
   </si>
@@ -112,6 +112,12 @@
   </si>
   <si>
     <t>Katamaa Diroo</t>
+  </si>
+  <si>
+    <t>Girmaa Masqalaa</t>
+  </si>
+  <si>
+    <t>Waktole Gutata</t>
   </si>
 </sst>
 </file>
@@ -919,12 +925,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -973,7 +978,7 @@
         <v>6</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E3">
         <v>151000</v>
@@ -1109,7 +1114,7 @@
         <v>14</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E11">
         <v>151000</v>
@@ -1245,7 +1250,7 @@
         <v>22</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E19">
         <v>49125</v>
@@ -1385,6 +1390,40 @@
       </c>
       <c r="E27">
         <v>51464</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B28">
+        <v>1027</v>
+      </c>
+      <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>46221</v>
+      </c>
+      <c r="B29">
+        <v>1028</v>
+      </c>
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="34">
   <si>
     <t>business_date</t>
   </si>
@@ -34,6 +34,9 @@
   </si>
   <si>
     <t>End_2026_achievement</t>
+  </si>
+  <si>
+    <t>NULL</t>
   </si>
   <si>
     <t>Geetu Bekela</t>
@@ -929,7 +932,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -951,14 +953,14 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>45854</v>
+      <c r="A2" t="s">
+        <v>5</v>
       </c>
       <c r="B2">
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -969,13 +971,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>45795</v>
+        <v>46223</v>
       </c>
       <c r="B3">
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>1000</v>
@@ -986,30 +988,30 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>45814</v>
+        <v>46223</v>
       </c>
       <c r="B4">
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E4">
         <v>151000</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>45795</v>
+      <c r="A5" t="s">
+        <v>5</v>
       </c>
       <c r="B5">
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1019,14 +1021,14 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>45854</v>
+      <c r="A6" t="s">
+        <v>5</v>
       </c>
       <c r="B6">
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1036,14 +1038,14 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>45795</v>
+      <c r="A7" t="s">
+        <v>5</v>
       </c>
       <c r="B7">
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1053,14 +1055,14 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>45795</v>
+      <c r="A8" t="s">
+        <v>5</v>
       </c>
       <c r="B8">
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1070,14 +1072,14 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>45795</v>
+      <c r="A9" t="s">
+        <v>5</v>
       </c>
       <c r="B9">
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1087,14 +1089,14 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>45818</v>
+      <c r="A10" t="s">
+        <v>5</v>
       </c>
       <c r="B10">
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1105,13 +1107,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>45844</v>
+        <v>46223</v>
       </c>
       <c r="B11">
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>1000</v>
@@ -1121,14 +1123,14 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>45935</v>
+      <c r="A12" t="s">
+        <v>5</v>
       </c>
       <c r="B12">
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1138,14 +1140,14 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>45849</v>
+      <c r="A13" t="s">
+        <v>5</v>
       </c>
       <c r="B13">
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1155,14 +1157,14 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>45862</v>
+      <c r="A14" t="s">
+        <v>5</v>
       </c>
       <c r="B14">
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1172,14 +1174,14 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>45846</v>
+      <c r="A15" t="s">
+        <v>5</v>
       </c>
       <c r="B15">
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1189,14 +1191,14 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>45977</v>
+      <c r="A16" t="s">
+        <v>5</v>
       </c>
       <c r="B16">
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1206,14 +1208,14 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <v>46000</v>
+      <c r="A17" t="s">
+        <v>5</v>
       </c>
       <c r="B17">
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1223,14 +1225,14 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>46004</v>
+      <c r="A18" t="s">
+        <v>5</v>
       </c>
       <c r="B18">
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1241,13 +1243,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>46164</v>
+        <v>46223</v>
       </c>
       <c r="B19">
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D19">
         <v>1000</v>
@@ -1257,14 +1259,14 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>46209</v>
+      <c r="A20" t="s">
+        <v>5</v>
       </c>
       <c r="B20">
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1274,14 +1276,14 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>46039</v>
+      <c r="A21" t="s">
+        <v>5</v>
       </c>
       <c r="B21">
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1291,14 +1293,14 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>46210</v>
+      <c r="A22" t="s">
+        <v>5</v>
       </c>
       <c r="B22">
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1308,14 +1310,14 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>46039</v>
+      <c r="A23" t="s">
+        <v>5</v>
       </c>
       <c r="B23">
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1325,14 +1327,14 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>46052</v>
+      <c r="A24" t="s">
+        <v>5</v>
       </c>
       <c r="B24">
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1342,14 +1344,14 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>46057</v>
+      <c r="A25" t="s">
+        <v>5</v>
       </c>
       <c r="B25">
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1359,14 +1361,14 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>46170</v>
+      <c r="A26" t="s">
+        <v>5</v>
       </c>
       <c r="B26">
         <v>1025</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1376,14 +1378,14 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <v>46170</v>
+      <c r="A27" t="s">
+        <v>5</v>
       </c>
       <c r="B27">
         <v>1026</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1393,14 +1395,14 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
-        <v>46213</v>
+      <c r="A28" t="s">
+        <v>5</v>
       </c>
       <c r="B28">
         <v>1027</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1410,14 +1412,14 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
-        <v>46221</v>
+      <c r="A29" t="s">
+        <v>5</v>
       </c>
       <c r="B29">
         <v>1028</v>
       </c>
       <c r="C29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D29">
         <v>0</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -34,6 +34,12 @@
   </si>
   <si>
     <t>End_2026_achievement</t>
+  </si>
+  <si>
+    <t>EGSA2027_Half_plan</t>
+  </si>
+  <si>
+    <t>EGSA2027_Half_achievement</t>
   </si>
   <si>
     <t>NULL</t>
@@ -928,14 +934,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -951,16 +959,22 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -968,8 +982,14 @@
       <c r="E2">
         <v>88893</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2">
+        <v>69000</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46223</v>
       </c>
@@ -977,7 +997,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>1000</v>
@@ -985,8 +1005,14 @@
       <c r="E3">
         <v>151000</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <v>69000</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46223</v>
       </c>
@@ -994,7 +1020,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>1000</v>
@@ -1002,16 +1028,22 @@
       <c r="E4">
         <v>151000</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <v>69000</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1019,16 +1051,22 @@
       <c r="E5">
         <v>84553</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <v>69000</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1036,16 +1074,22 @@
       <c r="E6">
         <v>61406</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <v>69000</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1053,16 +1097,22 @@
       <c r="E7">
         <v>151000</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <v>69000</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8">
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1070,16 +1120,22 @@
       <c r="E8">
         <v>59067</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <v>69000</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1087,16 +1143,22 @@
       <c r="E9">
         <v>145036</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <v>69000</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1104,8 +1166,14 @@
       <c r="E10">
         <v>61406</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <v>69000</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46223</v>
       </c>
@@ -1113,7 +1181,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D11">
         <v>1000</v>
@@ -1121,16 +1189,22 @@
       <c r="E11">
         <v>151000</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11">
+        <v>69000</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1138,16 +1212,22 @@
       <c r="E12">
         <v>59067</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12">
+        <v>69000</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B13">
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1155,16 +1235,22 @@
       <c r="E13">
         <v>153500</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13">
+        <v>69000</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B14">
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1172,16 +1258,22 @@
       <c r="E14">
         <v>101759</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14">
+        <v>69000</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B15">
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1189,16 +1281,22 @@
       <c r="E15">
         <v>102928</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15">
+        <v>69000</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B16">
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1206,16 +1304,22 @@
       <c r="E16">
         <v>184553</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16">
+        <v>69000</v>
+      </c>
+      <c r="G16">
+        <v>98000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B17">
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1223,16 +1327,22 @@
       <c r="E17">
         <v>54973</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17">
+        <v>69000</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B18">
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1240,8 +1350,14 @@
       <c r="E18">
         <v>73327</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <v>69000</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46223</v>
       </c>
@@ -1249,7 +1365,7 @@
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D19">
         <v>1000</v>
@@ -1257,16 +1373,22 @@
       <c r="E19">
         <v>49125</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19">
+        <v>69000</v>
+      </c>
+      <c r="G19">
+        <v>73000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B20">
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1274,16 +1396,22 @@
       <c r="E20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20">
+        <v>69000</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B21">
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1291,16 +1419,22 @@
       <c r="E21">
         <v>51464</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21">
+        <v>69000</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B22">
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1308,16 +1442,22 @@
       <c r="E22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F22">
+        <v>69000</v>
+      </c>
+      <c r="G22">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B23">
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1325,16 +1465,22 @@
       <c r="E23">
         <v>65500</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23">
+        <v>69000</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B24">
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1342,16 +1488,22 @@
       <c r="E24">
         <v>53803</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24">
+        <v>69000</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B25">
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1359,16 +1511,22 @@
       <c r="E25">
         <v>199000</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F25">
+        <v>69000</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B26">
         <v>1025</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1376,16 +1534,22 @@
       <c r="E26">
         <v>49125</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F26">
+        <v>69000</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B27">
         <v>1026</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1393,16 +1557,22 @@
       <c r="E27">
         <v>51464</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F27">
+        <v>69000</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B28">
         <v>1027</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1410,21 +1580,33 @@
       <c r="E28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F28">
+        <v>69000</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B29">
         <v>1028</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>69000</v>
+      </c>
+      <c r="G29">
         <v>0</v>
       </c>
     </row>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -36,10 +36,10 @@
     <t>End_2026_achievement</t>
   </si>
   <si>
-    <t>EGSA2027_Half_plan</t>
-  </si>
-  <si>
-    <t>EGSA2027_Half_achievement</t>
+    <t>EGSA2027_Half_Year_plan</t>
+  </si>
+  <si>
+    <t>EGSA2027_Half_Year_achievement</t>
   </si>
   <si>
     <t>NULL</t>
@@ -938,9 +938,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -1056,8 +1056,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>7</v>
+      <c r="A6" s="1">
+        <v>46228</v>
       </c>
       <c r="B6">
         <v>1005</v>
@@ -1066,7 +1066,7 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E6">
         <v>61406</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -1240,8 +1240,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>7</v>
+      <c r="A14" s="1">
+        <v>46228</v>
       </c>
       <c r="B14">
         <v>1013</v>
@@ -1250,7 +1250,7 @@
         <v>20</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E14">
         <v>101759</v>
@@ -1424,8 +1424,8 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>7</v>
+      <c r="A22" s="1">
+        <v>46228</v>
       </c>
       <c r="B22">
         <v>1021</v>
@@ -1434,7 +1434,7 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1443,7 +1443,7 @@
         <v>69000</v>
       </c>
       <c r="G22">
-        <v>13000</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -42,16 +42,16 @@
     <t>EGSA2027_Half_Year_achievement</t>
   </si>
   <si>
+    <t>Geetu Bekela</t>
+  </si>
+  <si>
+    <t>Walfana Megersa</t>
+  </si>
+  <si>
+    <t>Fayisa Badhu</t>
+  </si>
+  <si>
     <t>NULL</t>
-  </si>
-  <si>
-    <t>Geetu Bekela</t>
-  </si>
-  <si>
-    <t>Walfana Megersa</t>
-  </si>
-  <si>
-    <t>Fayisa Badhu</t>
   </si>
   <si>
     <t>Silash Dabesa</t>
@@ -938,6 +938,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -964,17 +965,17 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>7</v>
+      <c r="A2" s="1">
+        <v>46229</v>
       </c>
       <c r="B2">
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E2">
         <v>88893</v>
@@ -994,7 +995,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>1000</v>
@@ -1017,7 +1018,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>1000</v>
@@ -1034,7 +1035,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>1004</v>
@@ -1080,7 +1081,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7">
         <v>1006</v>
@@ -1103,7 +1104,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>1007</v>
@@ -1126,7 +1127,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <v>1008</v>
@@ -1149,7 +1150,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>1009</v>
@@ -1195,7 +1196,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B12">
         <v>1011</v>
@@ -1218,7 +1219,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B13">
         <v>1012</v>
@@ -1264,7 +1265,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B15">
         <v>1014</v>
@@ -1287,7 +1288,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B16">
         <v>1015</v>
@@ -1310,7 +1311,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B17">
         <v>1016</v>
@@ -1333,7 +1334,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B18">
         <v>1017</v>
@@ -1379,7 +1380,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B20">
         <v>1019</v>
@@ -1402,7 +1403,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B21">
         <v>1020</v>
@@ -1448,7 +1449,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B23">
         <v>1022</v>
@@ -1471,7 +1472,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B24">
         <v>1023</v>
@@ -1494,7 +1495,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B25">
         <v>1024</v>
@@ -1517,7 +1518,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B26">
         <v>1025</v>
@@ -1540,7 +1541,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B27">
         <v>1026</v>
@@ -1563,7 +1564,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B28">
         <v>1027</v>
@@ -1586,7 +1587,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B29">
         <v>1028</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -938,7 +938,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1080,8 +1081,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>10</v>
+      <c r="A7" s="1">
+        <v>46230</v>
       </c>
       <c r="B7">
         <v>1006</v>
@@ -1090,7 +1091,7 @@
         <v>13</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E7">
         <v>151000</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -938,8 +938,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1127,8 +1127,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>10</v>
+      <c r="A9" s="1">
+        <v>46230</v>
       </c>
       <c r="B9">
         <v>1008</v>
@@ -1137,7 +1137,7 @@
         <v>15</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E9">
         <v>145036</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -938,8 +938,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1196,8 +1194,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>10</v>
+      <c r="A12" s="1">
+        <v>46230</v>
       </c>
       <c r="B12">
         <v>1011</v>
@@ -1206,7 +1204,7 @@
         <v>18</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E12">
         <v>59067</v>
@@ -1518,8 +1516,8 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>10</v>
+      <c r="A26" s="1">
+        <v>46230</v>
       </c>
       <c r="B26">
         <v>1025</v>
@@ -1528,7 +1526,7 @@
         <v>32</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E26">
         <v>49125</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -1447,8 +1447,8 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>10</v>
+      <c r="A23" s="1">
+        <v>46231</v>
       </c>
       <c r="B23">
         <v>1022</v>
@@ -1457,7 +1457,7 @@
         <v>29</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E23">
         <v>65500</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -1217,8 +1217,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>10</v>
+      <c r="A13" s="1">
+        <v>46231</v>
       </c>
       <c r="B13">
         <v>1012</v>
@@ -1227,7 +1227,7 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E13">
         <v>153500</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -1332,8 +1332,8 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>10</v>
+      <c r="A18" s="1">
+        <v>46231</v>
       </c>
       <c r="B18">
         <v>1017</v>
@@ -1342,7 +1342,7 @@
         <v>24</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E18">
         <v>73327</v>
@@ -1562,8 +1562,8 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>10</v>
+      <c r="A28" s="1">
+        <v>46231</v>
       </c>
       <c r="B28">
         <v>1027</v>
@@ -1572,7 +1572,7 @@
         <v>34</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1581,7 +1581,7 @@
         <v>69000</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -1263,8 +1263,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>10</v>
+      <c r="A15" s="1">
+        <v>46231</v>
       </c>
       <c r="B15">
         <v>1014</v>
@@ -1273,7 +1273,7 @@
         <v>21</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E15">
         <v>102928</v>
@@ -1585,8 +1585,8 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>10</v>
+      <c r="A29" s="1">
+        <v>46231</v>
       </c>
       <c r="B29">
         <v>1028</v>
@@ -1595,7 +1595,7 @@
         <v>35</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1604,7 +1604,7 @@
         <v>69000</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>13000</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -938,6 +938,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1029,7 +1031,7 @@
         <v>69000</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1075,7 +1077,7 @@
         <v>69000</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1098,7 +1100,7 @@
         <v>69000</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1144,7 +1146,7 @@
         <v>69000</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1190,7 +1192,7 @@
         <v>69000</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -934,12 +934,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1288,8 +1286,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>10</v>
+      <c r="A16" s="1">
+        <v>46232</v>
       </c>
       <c r="B16">
         <v>1015</v>
@@ -1298,7 +1296,7 @@
         <v>22</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E16">
         <v>184553</v>
@@ -1307,47 +1305,47 @@
         <v>69000</v>
       </c>
       <c r="G16">
-        <v>98000</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B17">
+        <v>1015</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17">
+        <v>1000</v>
+      </c>
+      <c r="E17">
+        <v>184553</v>
+      </c>
+      <c r="F17">
+        <v>69000</v>
+      </c>
+      <c r="G17">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>10</v>
       </c>
-      <c r="B17">
+      <c r="B18">
         <v>1016</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>23</v>
       </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
         <v>54973</v>
-      </c>
-      <c r="F17">
-        <v>69000</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>46231</v>
-      </c>
-      <c r="B18">
-        <v>1017</v>
-      </c>
-      <c r="C18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18">
-        <v>1000</v>
-      </c>
-      <c r="E18">
-        <v>73327</v>
       </c>
       <c r="F18">
         <v>69000</v>
@@ -1358,48 +1356,48 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B19">
+        <v>1017</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19">
+        <v>1000</v>
+      </c>
+      <c r="E19">
+        <v>73327</v>
+      </c>
+      <c r="F19">
+        <v>69000</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
         <v>46223</v>
       </c>
-      <c r="B19">
+      <c r="B20">
         <v>1018</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C20" t="s">
         <v>25</v>
       </c>
-      <c r="D19">
-        <v>1000</v>
-      </c>
-      <c r="E19">
+      <c r="D20">
+        <v>1000</v>
+      </c>
+      <c r="E20">
         <v>49125</v>
       </c>
-      <c r="F19">
-        <v>69000</v>
-      </c>
-      <c r="G19">
+      <c r="F20">
+        <v>69000</v>
+      </c>
+      <c r="G20">
         <v>73000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20">
-        <v>1019</v>
-      </c>
-      <c r="C20" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>69000</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1407,85 +1405,85 @@
         <v>10</v>
       </c>
       <c r="B21">
+        <v>1019</v>
+      </c>
+      <c r="C21" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>69000</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22">
         <v>1020</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>27</v>
       </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
         <v>51464</v>
       </c>
-      <c r="F21">
-        <v>69000</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>46228</v>
-      </c>
-      <c r="B22">
-        <v>1021</v>
-      </c>
-      <c r="C22" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22">
-        <v>1000</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
       <c r="F22">
         <v>69000</v>
       </c>
       <c r="G22">
-        <v>27000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
+        <v>46228</v>
+      </c>
+      <c r="B23">
+        <v>1021</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23">
+        <v>1000</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>69000</v>
+      </c>
+      <c r="G23">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
         <v>46231</v>
       </c>
-      <c r="B23">
+      <c r="B24">
         <v>1022</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C24" t="s">
         <v>29</v>
       </c>
-      <c r="D23">
-        <v>1000</v>
-      </c>
-      <c r="E23">
+      <c r="D24">
+        <v>1000</v>
+      </c>
+      <c r="E24">
         <v>65500</v>
-      </c>
-      <c r="F23">
-        <v>69000</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24">
-        <v>1023</v>
-      </c>
-      <c r="C24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>53803</v>
       </c>
       <c r="F24">
         <v>69000</v>
@@ -1499,91 +1497,91 @@
         <v>10</v>
       </c>
       <c r="B25">
+        <v>1023</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>53803</v>
+      </c>
+      <c r="F25">
+        <v>69000</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26">
         <v>1024</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>31</v>
       </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
         <v>199000</v>
       </c>
-      <c r="F25">
-        <v>69000</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+      <c r="F26">
+        <v>69000</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
         <v>46230</v>
       </c>
-      <c r="B26">
+      <c r="B27">
         <v>1025</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C27" t="s">
         <v>32</v>
       </c>
-      <c r="D26">
-        <v>1000</v>
-      </c>
-      <c r="E26">
+      <c r="D27">
+        <v>1000</v>
+      </c>
+      <c r="E27">
         <v>49125</v>
       </c>
-      <c r="F26">
-        <v>69000</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="F27">
+        <v>69000</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>10</v>
       </c>
-      <c r="B27">
+      <c r="B28">
         <v>1026</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>33</v>
       </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27">
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
         <v>51464</v>
       </c>
-      <c r="F27">
-        <v>69000</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
-        <v>46231</v>
-      </c>
-      <c r="B28">
-        <v>1027</v>
-      </c>
-      <c r="C28" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28">
-        <v>1000</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
       <c r="F28">
         <v>69000</v>
       </c>
       <c r="G28">
-        <v>40000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1591,21 +1589,44 @@
         <v>46231</v>
       </c>
       <c r="B29">
+        <v>1027</v>
+      </c>
+      <c r="C29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29">
+        <v>1000</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>69000</v>
+      </c>
+      <c r="G29">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B30">
         <v>1028</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C30" t="s">
         <v>35</v>
       </c>
-      <c r="D29">
-        <v>1000</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>69000</v>
-      </c>
-      <c r="G29">
+      <c r="D30">
+        <v>1000</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>69000</v>
+      </c>
+      <c r="G30">
         <v>13000</v>
       </c>
     </row>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -934,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1309,43 +1309,43 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <v>46232</v>
+      <c r="A17" t="s">
+        <v>10</v>
       </c>
       <c r="B17">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>184553</v>
+        <v>54973</v>
       </c>
       <c r="F17">
         <v>69000</v>
       </c>
       <c r="G17">
-        <v>99000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>10</v>
+      <c r="A18" s="1">
+        <v>46231</v>
       </c>
       <c r="B18">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E18">
-        <v>54973</v>
+        <v>73327</v>
       </c>
       <c r="F18">
         <v>69000</v>
@@ -1356,48 +1356,48 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>46231</v>
+        <v>46223</v>
       </c>
       <c r="B19">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D19">
         <v>1000</v>
       </c>
       <c r="E19">
-        <v>73327</v>
+        <v>49125</v>
       </c>
       <c r="F19">
         <v>69000</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>73000</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>46223</v>
+      <c r="A20" t="s">
+        <v>10</v>
       </c>
       <c r="B20">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>49125</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>69000</v>
       </c>
       <c r="G20">
-        <v>73000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1405,16 +1405,16 @@
         <v>10</v>
       </c>
       <c r="B21">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>51464</v>
       </c>
       <c r="F21">
         <v>69000</v>
@@ -1424,66 +1424,66 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>10</v>
+      <c r="A22" s="1">
+        <v>46228</v>
       </c>
       <c r="B22">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E22">
-        <v>51464</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>69000</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="B23">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D23">
         <v>1000</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>65500</v>
       </c>
       <c r="F23">
         <v>69000</v>
       </c>
       <c r="G23">
-        <v>27000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>46231</v>
+      <c r="A24" t="s">
+        <v>10</v>
       </c>
       <c r="B24">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>65500</v>
+        <v>53803</v>
       </c>
       <c r="F24">
         <v>69000</v>
@@ -1497,16 +1497,16 @@
         <v>10</v>
       </c>
       <c r="B25">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>53803</v>
+        <v>199000</v>
       </c>
       <c r="F25">
         <v>69000</v>
@@ -1516,43 +1516,43 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B26">
+        <v>1025</v>
+      </c>
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26">
+        <v>1000</v>
+      </c>
+      <c r="E26">
+        <v>49125</v>
+      </c>
+      <c r="F26">
+        <v>69000</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>10</v>
       </c>
-      <c r="B26">
-        <v>1024</v>
-      </c>
-      <c r="C26" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>199000</v>
-      </c>
-      <c r="F26">
-        <v>69000</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <v>46230</v>
-      </c>
       <c r="B27">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>49125</v>
+        <v>51464</v>
       </c>
       <c r="F27">
         <v>69000</v>
@@ -1562,26 +1562,26 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>10</v>
+      <c r="A28" s="1">
+        <v>46231</v>
       </c>
       <c r="B28">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E28">
-        <v>51464</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>69000</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1589,10 +1589,10 @@
         <v>46231</v>
       </c>
       <c r="B29">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D29">
         <v>1000</v>
@@ -1604,29 +1604,6 @@
         <v>69000</v>
       </c>
       <c r="G29">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
-        <v>46231</v>
-      </c>
-      <c r="B30">
-        <v>1028</v>
-      </c>
-      <c r="C30" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30">
-        <v>1000</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>69000</v>
-      </c>
-      <c r="G30">
         <v>13000</v>
       </c>
     </row>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -938,6 +938,9 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -938,8 +938,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1105,8 +1105,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>10</v>
+      <c r="A8" s="1">
+        <v>46232</v>
       </c>
       <c r="B8">
         <v>1007</v>
@@ -1115,7 +1115,7 @@
         <v>14</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E8">
         <v>59067</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -938,9 +938,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1151,8 +1148,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>10</v>
+      <c r="A10" s="1">
+        <v>46233</v>
       </c>
       <c r="B10">
         <v>1009</v>
@@ -1161,7 +1158,7 @@
         <v>16</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E10">
         <v>61406</v>
@@ -1381,8 +1378,8 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>10</v>
+      <c r="A20" s="1">
+        <v>46233</v>
       </c>
       <c r="B20">
         <v>1019</v>
@@ -1391,7 +1388,7 @@
         <v>26</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1404,8 +1401,8 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>10</v>
+      <c r="A21" s="1">
+        <v>46233</v>
       </c>
       <c r="B21">
         <v>1020</v>
@@ -1414,7 +1411,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E21">
         <v>51464</v>
@@ -1542,8 +1539,8 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>10</v>
+      <c r="A27" s="1">
+        <v>46233</v>
       </c>
       <c r="B27">
         <v>1026</v>
@@ -1552,7 +1549,7 @@
         <v>33</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E27">
         <v>51464</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -1470,8 +1470,8 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>10</v>
+      <c r="A24" s="1">
+        <v>46233</v>
       </c>
       <c r="B24">
         <v>1023</v>
@@ -1480,7 +1480,7 @@
         <v>30</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E24">
         <v>53803</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -1493,8 +1493,8 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>10</v>
+      <c r="A25" s="1">
+        <v>46233</v>
       </c>
       <c r="B25">
         <v>1024</v>
@@ -1503,7 +1503,7 @@
         <v>31</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E25">
         <v>199000</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -1309,8 +1309,8 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>10</v>
+      <c r="A17" s="1">
+        <v>46237</v>
       </c>
       <c r="B17">
         <v>1016</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -938,6 +938,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1319,7 +1320,7 @@
         <v>23</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E17">
         <v>54973</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="37">
   <si>
     <t>business_date</t>
   </si>
@@ -42,6 +42,9 @@
     <t>EGSA2027_Half_Year_achievement</t>
   </si>
   <si>
+    <t>NULL</t>
+  </si>
+  <si>
     <t>Geetu Bekela</t>
   </si>
   <si>
@@ -51,9 +54,6 @@
     <t>Fayisa Badhu</t>
   </si>
   <si>
-    <t>NULL</t>
-  </si>
-  <si>
     <t>Silash Dabesa</t>
   </si>
   <si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t>Waktole Gutata</t>
+  </si>
+  <si>
+    <t>Tarreessaa Wadaajoo</t>
   </si>
 </sst>
 </file>
@@ -934,11 +937,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -965,17 +972,17 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>46229</v>
+      <c r="A2" t="s">
+        <v>7</v>
       </c>
       <c r="B2">
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>88893</v>
@@ -984,21 +991,21 @@
         <v>69000</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>46223</v>
+      <c r="A3" t="s">
+        <v>7</v>
       </c>
       <c r="B3">
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>151000</v>
@@ -1007,21 +1014,21 @@
         <v>69000</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>46223</v>
+      <c r="A4" t="s">
+        <v>7</v>
       </c>
       <c r="B4">
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>151000</v>
@@ -1030,12 +1037,12 @@
         <v>69000</v>
       </c>
       <c r="G4">
-        <v>10000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>1004</v>
@@ -1058,7 +1065,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>46228</v>
+        <v>46259</v>
       </c>
       <c r="B6">
         <v>1005</v>
@@ -1076,231 +1083,231 @@
         <v>69000</v>
       </c>
       <c r="G6">
-        <v>10000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>46230</v>
+      <c r="A7" t="s">
+        <v>7</v>
       </c>
       <c r="B7">
+        <v>1005</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>61406</v>
+      </c>
+      <c r="F7">
+        <v>69000</v>
+      </c>
+      <c r="G7">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
         <v>1006</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="D7">
-        <v>1000</v>
-      </c>
-      <c r="E7">
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>151000</v>
       </c>
-      <c r="F7">
-        <v>69000</v>
-      </c>
-      <c r="G7">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>46232</v>
-      </c>
-      <c r="B8">
+      <c r="F8">
+        <v>69000</v>
+      </c>
+      <c r="G8">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
         <v>1007</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>14</v>
       </c>
-      <c r="D8">
-        <v>1000</v>
-      </c>
-      <c r="E8">
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>59067</v>
       </c>
-      <c r="F8">
-        <v>69000</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>46230</v>
-      </c>
-      <c r="B9">
-        <v>1008</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9">
-        <v>1000</v>
-      </c>
-      <c r="E9">
-        <v>145036</v>
-      </c>
       <c r="F9">
         <v>69000</v>
       </c>
       <c r="G9">
-        <v>10000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>46233</v>
+        <v>46258</v>
       </c>
       <c r="B10">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>1000</v>
       </c>
       <c r="E10">
-        <v>61406</v>
+        <v>145036</v>
       </c>
       <c r="F10">
         <v>69000</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>46223</v>
+      <c r="A11" t="s">
+        <v>7</v>
       </c>
       <c r="B11">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>151000</v>
+        <v>145036</v>
       </c>
       <c r="F11">
         <v>69000</v>
       </c>
       <c r="G11">
-        <v>20000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>46230</v>
+        <v>46258</v>
       </c>
       <c r="B12">
+        <v>1009</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <v>1000</v>
+      </c>
+      <c r="E12">
+        <v>61406</v>
+      </c>
+      <c r="F12">
+        <v>69000</v>
+      </c>
+      <c r="G12">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13">
+        <v>1009</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>61406</v>
+      </c>
+      <c r="F13">
+        <v>69000</v>
+      </c>
+      <c r="G13">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>1010</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>151000</v>
+      </c>
+      <c r="F14">
+        <v>69000</v>
+      </c>
+      <c r="G14">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15">
         <v>1011</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C15" t="s">
         <v>18</v>
       </c>
-      <c r="D12">
-        <v>1000</v>
-      </c>
-      <c r="E12">
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
         <v>59067</v>
       </c>
-      <c r="F12">
-        <v>69000</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>46231</v>
-      </c>
-      <c r="B13">
+      <c r="F15">
+        <v>69000</v>
+      </c>
+      <c r="G15">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16">
         <v>1012</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C16" t="s">
         <v>19</v>
       </c>
-      <c r="D13">
-        <v>1000</v>
-      </c>
-      <c r="E13">
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
         <v>153500</v>
-      </c>
-      <c r="F13">
-        <v>69000</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>46228</v>
-      </c>
-      <c r="B14">
-        <v>1013</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14">
-        <v>1000</v>
-      </c>
-      <c r="E14">
-        <v>101759</v>
-      </c>
-      <c r="F14">
-        <v>69000</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>46231</v>
-      </c>
-      <c r="B15">
-        <v>1014</v>
-      </c>
-      <c r="C15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15">
-        <v>1000</v>
-      </c>
-      <c r="E15">
-        <v>102928</v>
-      </c>
-      <c r="F15">
-        <v>69000</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>46232</v>
-      </c>
-      <c r="B16">
-        <v>1015</v>
-      </c>
-      <c r="C16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16">
-        <v>1000</v>
-      </c>
-      <c r="E16">
-        <v>184553</v>
       </c>
       <c r="F16">
         <v>69000</v>
@@ -1311,301 +1318,462 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>46237</v>
+        <v>46259</v>
       </c>
       <c r="B17">
+        <v>1013</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17">
+        <v>1000</v>
+      </c>
+      <c r="E17">
+        <v>101759</v>
+      </c>
+      <c r="F17">
+        <v>69000</v>
+      </c>
+      <c r="G17">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18">
+        <v>1013</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>101759</v>
+      </c>
+      <c r="F18">
+        <v>69000</v>
+      </c>
+      <c r="G18">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19">
+        <v>1014</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>102928</v>
+      </c>
+      <c r="F19">
+        <v>69000</v>
+      </c>
+      <c r="G19">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20">
+        <v>1015</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>184553</v>
+      </c>
+      <c r="F20">
+        <v>69000</v>
+      </c>
+      <c r="G20">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21">
         <v>1016</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C21" t="s">
         <v>23</v>
       </c>
-      <c r="D17">
-        <v>1000</v>
-      </c>
-      <c r="E17">
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
         <v>54973</v>
       </c>
-      <c r="F17">
-        <v>69000</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>46231</v>
-      </c>
-      <c r="B18">
+      <c r="F21">
+        <v>69000</v>
+      </c>
+      <c r="G21">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22">
         <v>1017</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C22" t="s">
         <v>24</v>
       </c>
-      <c r="D18">
-        <v>1000</v>
-      </c>
-      <c r="E18">
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
         <v>73327</v>
       </c>
-      <c r="F18">
-        <v>69000</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
-        <v>46223</v>
-      </c>
-      <c r="B19">
+      <c r="F22">
+        <v>69000</v>
+      </c>
+      <c r="G22">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23">
         <v>1018</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C23" t="s">
         <v>25</v>
       </c>
-      <c r="D19">
-        <v>1000</v>
-      </c>
-      <c r="E19">
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
         <v>49125</v>
       </c>
-      <c r="F19">
-        <v>69000</v>
-      </c>
-      <c r="G19">
-        <v>73000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>46233</v>
-      </c>
-      <c r="B20">
+      <c r="F23">
+        <v>69000</v>
+      </c>
+      <c r="G23">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24">
         <v>1019</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C24" t="s">
         <v>26</v>
       </c>
-      <c r="D20">
-        <v>1000</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>69000</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>46233</v>
-      </c>
-      <c r="B21">
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>69000</v>
+      </c>
+      <c r="G24">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25">
         <v>1020</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C25" t="s">
         <v>27</v>
       </c>
-      <c r="D21">
-        <v>1000</v>
-      </c>
-      <c r="E21">
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
         <v>51464</v>
       </c>
-      <c r="F21">
-        <v>69000</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>46228</v>
-      </c>
-      <c r="B22">
-        <v>1021</v>
-      </c>
-      <c r="C22" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22">
-        <v>1000</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>69000</v>
-      </c>
-      <c r="G22">
-        <v>27000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>46231</v>
-      </c>
-      <c r="B23">
-        <v>1022</v>
-      </c>
-      <c r="C23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23">
-        <v>1000</v>
-      </c>
-      <c r="E23">
-        <v>65500</v>
-      </c>
-      <c r="F23">
-        <v>69000</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>46233</v>
-      </c>
-      <c r="B24">
-        <v>1023</v>
-      </c>
-      <c r="C24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24">
-        <v>1000</v>
-      </c>
-      <c r="E24">
-        <v>53803</v>
-      </c>
-      <c r="F24">
-        <v>69000</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>46233</v>
-      </c>
-      <c r="B25">
-        <v>1024</v>
-      </c>
-      <c r="C25" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25">
-        <v>1000</v>
-      </c>
-      <c r="E25">
-        <v>199000</v>
-      </c>
       <c r="F25">
         <v>69000</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>46230</v>
+        <v>46258</v>
       </c>
       <c r="B26">
+        <v>1021</v>
+      </c>
+      <c r="C26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26">
+        <v>1000</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>69000</v>
+      </c>
+      <c r="G26">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27">
+        <v>1021</v>
+      </c>
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>69000</v>
+      </c>
+      <c r="G27">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28">
+        <v>1022</v>
+      </c>
+      <c r="C28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>65500</v>
+      </c>
+      <c r="F28">
+        <v>69000</v>
+      </c>
+      <c r="G28">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29">
+        <v>1023</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>53803</v>
+      </c>
+      <c r="F29">
+        <v>69000</v>
+      </c>
+      <c r="G29">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30">
+        <v>1024</v>
+      </c>
+      <c r="C30" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>199000</v>
+      </c>
+      <c r="F30">
+        <v>69000</v>
+      </c>
+      <c r="G30">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31">
         <v>1025</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C31" t="s">
         <v>32</v>
       </c>
-      <c r="D26">
-        <v>1000</v>
-      </c>
-      <c r="E26">
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
         <v>49125</v>
       </c>
-      <c r="F26">
-        <v>69000</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <v>46233</v>
-      </c>
-      <c r="B27">
+      <c r="F31">
+        <v>69000</v>
+      </c>
+      <c r="G31">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32">
         <v>1026</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C32" t="s">
         <v>33</v>
       </c>
-      <c r="D27">
-        <v>1000</v>
-      </c>
-      <c r="E27">
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
         <v>51464</v>
       </c>
-      <c r="F27">
-        <v>69000</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
-        <v>46231</v>
-      </c>
-      <c r="B28">
+      <c r="F32">
+        <v>69000</v>
+      </c>
+      <c r="G32">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B33">
         <v>1027</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C33" t="s">
         <v>34</v>
       </c>
-      <c r="D28">
-        <v>1000</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>69000</v>
-      </c>
-      <c r="G28">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
-        <v>46231</v>
-      </c>
-      <c r="B29">
+      <c r="D33">
+        <v>1000</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>69000</v>
+      </c>
+      <c r="G33">
+        <v>41000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34">
+        <v>1027</v>
+      </c>
+      <c r="C34" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>69000</v>
+      </c>
+      <c r="G34">
+        <v>41000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35">
         <v>1028</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C35" t="s">
         <v>35</v>
       </c>
-      <c r="D29">
-        <v>1000</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>69000</v>
-      </c>
-      <c r="G29">
-        <v>13000</v>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>69000</v>
+      </c>
+      <c r="G35">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36">
+        <v>1029</v>
+      </c>
+      <c r="C36" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>69000</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="37">
   <si>
     <t>business_date</t>
   </si>
@@ -937,14 +937,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1041,8 +1040,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
+      <c r="A5" s="1">
+        <v>46260</v>
       </c>
       <c r="B5">
         <v>1004</v>
@@ -1051,7 +1050,7 @@
         <v>11</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E5">
         <v>84553</v>
@@ -1064,31 +1063,31 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>1004</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>84553</v>
+      </c>
+      <c r="F6">
+        <v>69000</v>
+      </c>
+      <c r="G6">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>46259</v>
-      </c>
-      <c r="B6">
-        <v>1005</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6">
-        <v>1000</v>
-      </c>
-      <c r="E6">
-        <v>61406</v>
-      </c>
-      <c r="F6">
-        <v>69000</v>
-      </c>
-      <c r="G6">
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>7</v>
       </c>
       <c r="B7">
         <v>1005</v>
@@ -1097,7 +1096,7 @@
         <v>12</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E7">
         <v>61406</v>
@@ -1114,16 +1113,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>151000</v>
+        <v>61406</v>
       </c>
       <c r="F8">
         <v>69000</v>
@@ -1137,50 +1136,50 @@
         <v>7</v>
       </c>
       <c r="B9">
+        <v>1006</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>151000</v>
+      </c>
+      <c r="F9">
+        <v>69000</v>
+      </c>
+      <c r="G9">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10">
         <v>1007</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>14</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>59067</v>
       </c>
-      <c r="F9">
-        <v>69000</v>
-      </c>
-      <c r="G9">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+      <c r="F10">
+        <v>69000</v>
+      </c>
+      <c r="G10">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
         <v>46258</v>
-      </c>
-      <c r="B10">
-        <v>1008</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10">
-        <v>1000</v>
-      </c>
-      <c r="E10">
-        <v>145036</v>
-      </c>
-      <c r="F10">
-        <v>69000</v>
-      </c>
-      <c r="G10">
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>7</v>
       </c>
       <c r="B11">
         <v>1008</v>
@@ -1189,7 +1188,7 @@
         <v>15</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E11">
         <v>145036</v>
@@ -1202,31 +1201,31 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>145036</v>
+      </c>
+      <c r="F12">
+        <v>69000</v>
+      </c>
+      <c r="G12">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
         <v>46258</v>
-      </c>
-      <c r="B12">
-        <v>1009</v>
-      </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12">
-        <v>1000</v>
-      </c>
-      <c r="E12">
-        <v>61406</v>
-      </c>
-      <c r="F12">
-        <v>69000</v>
-      </c>
-      <c r="G12">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>7</v>
       </c>
       <c r="B13">
         <v>1009</v>
@@ -1235,7 +1234,7 @@
         <v>16</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E13">
         <v>61406</v>
@@ -1252,22 +1251,22 @@
         <v>7</v>
       </c>
       <c r="B14">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>151000</v>
+        <v>61406</v>
       </c>
       <c r="F14">
         <v>69000</v>
       </c>
       <c r="G14">
-        <v>21000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1275,22 +1274,22 @@
         <v>7</v>
       </c>
       <c r="B15">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>59067</v>
+        <v>151000</v>
       </c>
       <c r="F15">
         <v>69000</v>
       </c>
       <c r="G15">
-        <v>1000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1298,50 +1297,50 @@
         <v>7</v>
       </c>
       <c r="B16">
+        <v>1011</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>59067</v>
+      </c>
+      <c r="F16">
+        <v>69000</v>
+      </c>
+      <c r="G16">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17">
         <v>1012</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>19</v>
       </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
         <v>153500</v>
       </c>
-      <c r="F16">
-        <v>69000</v>
-      </c>
-      <c r="G16">
+      <c r="F17">
+        <v>69000</v>
+      </c>
+      <c r="G17">
         <v>99000</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
         <v>46259</v>
-      </c>
-      <c r="B17">
-        <v>1013</v>
-      </c>
-      <c r="C17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17">
-        <v>1000</v>
-      </c>
-      <c r="E17">
-        <v>101759</v>
-      </c>
-      <c r="F17">
-        <v>69000</v>
-      </c>
-      <c r="G17">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>7</v>
       </c>
       <c r="B18">
         <v>1013</v>
@@ -1350,7 +1349,7 @@
         <v>20</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E18">
         <v>101759</v>
@@ -1367,16 +1366,16 @@
         <v>7</v>
       </c>
       <c r="B19">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>102928</v>
+        <v>101759</v>
       </c>
       <c r="F19">
         <v>69000</v>
@@ -1390,22 +1389,22 @@
         <v>7</v>
       </c>
       <c r="B20">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>184553</v>
+        <v>102928</v>
       </c>
       <c r="F20">
         <v>69000</v>
       </c>
       <c r="G20">
-        <v>100000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1413,22 +1412,22 @@
         <v>7</v>
       </c>
       <c r="B21">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>54973</v>
+        <v>184553</v>
       </c>
       <c r="F21">
         <v>69000</v>
       </c>
       <c r="G21">
-        <v>1000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1436,16 +1435,16 @@
         <v>7</v>
       </c>
       <c r="B22">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>73327</v>
+        <v>54973</v>
       </c>
       <c r="F22">
         <v>69000</v>
@@ -1459,22 +1458,22 @@
         <v>7</v>
       </c>
       <c r="B23">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>49125</v>
+        <v>73327</v>
       </c>
       <c r="F23">
         <v>69000</v>
       </c>
       <c r="G23">
-        <v>74000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -1482,22 +1481,22 @@
         <v>7</v>
       </c>
       <c r="B24">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>49125</v>
       </c>
       <c r="F24">
         <v>69000</v>
       </c>
       <c r="G24">
-        <v>1000</v>
+        <v>74000</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1505,50 +1504,50 @@
         <v>7</v>
       </c>
       <c r="B25">
+        <v>1019</v>
+      </c>
+      <c r="C25" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>69000</v>
+      </c>
+      <c r="G25">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26">
         <v>1020</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>27</v>
       </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
         <v>51464</v>
       </c>
-      <c r="F25">
-        <v>69000</v>
-      </c>
-      <c r="G25">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+      <c r="F26">
+        <v>69000</v>
+      </c>
+      <c r="G26">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
         <v>46258</v>
-      </c>
-      <c r="B26">
-        <v>1021</v>
-      </c>
-      <c r="C26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26">
-        <v>1000</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>69000</v>
-      </c>
-      <c r="G26">
-        <v>39000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>7</v>
       </c>
       <c r="B27">
         <v>1021</v>
@@ -1557,7 +1556,7 @@
         <v>28</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1574,22 +1573,22 @@
         <v>7</v>
       </c>
       <c r="B28">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>65500</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>69000</v>
       </c>
       <c r="G28">
-        <v>1000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1597,16 +1596,16 @@
         <v>7</v>
       </c>
       <c r="B29">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>53803</v>
+        <v>65500</v>
       </c>
       <c r="F29">
         <v>69000</v>
@@ -1620,16 +1619,16 @@
         <v>7</v>
       </c>
       <c r="B30">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>199000</v>
+        <v>53803</v>
       </c>
       <c r="F30">
         <v>69000</v>
@@ -1643,16 +1642,16 @@
         <v>7</v>
       </c>
       <c r="B31">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>49125</v>
+        <v>199000</v>
       </c>
       <c r="F31">
         <v>69000</v>
@@ -1666,50 +1665,50 @@
         <v>7</v>
       </c>
       <c r="B32">
+        <v>1025</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>49125</v>
+      </c>
+      <c r="F32">
+        <v>69000</v>
+      </c>
+      <c r="G32">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33">
         <v>1026</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>33</v>
       </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32">
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
         <v>51464</v>
       </c>
-      <c r="F32">
-        <v>69000</v>
-      </c>
-      <c r="G32">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
+      <c r="F33">
+        <v>69000</v>
+      </c>
+      <c r="G33">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
         <v>46259</v>
-      </c>
-      <c r="B33">
-        <v>1027</v>
-      </c>
-      <c r="C33" t="s">
-        <v>34</v>
-      </c>
-      <c r="D33">
-        <v>1000</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>69000</v>
-      </c>
-      <c r="G33">
-        <v>41000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>7</v>
       </c>
       <c r="B34">
         <v>1027</v>
@@ -1718,7 +1717,7 @@
         <v>34</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1735,10 +1734,10 @@
         <v>7</v>
       </c>
       <c r="B35">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1750,7 +1749,7 @@
         <v>69000</v>
       </c>
       <c r="G35">
-        <v>14000</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -1758,21 +1757,44 @@
         <v>7</v>
       </c>
       <c r="B36">
+        <v>1028</v>
+      </c>
+      <c r="C36" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>69000</v>
+      </c>
+      <c r="G36">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37">
         <v>1029</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C37" t="s">
         <v>36</v>
       </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>69000</v>
-      </c>
-      <c r="G36">
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>69000</v>
+      </c>
+      <c r="G37">
         <v>0</v>
       </c>
     </row>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
   <si>
     <t>business_date</t>
   </si>
@@ -937,13 +937,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1063,43 +1064,43 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>7</v>
+      <c r="A6" s="1">
+        <v>46259</v>
       </c>
       <c r="B6">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E6">
-        <v>84553</v>
+        <v>61406</v>
       </c>
       <c r="F6">
         <v>69000</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>46259</v>
+      <c r="A7" t="s">
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>61406</v>
+        <v>151000</v>
       </c>
       <c r="F7">
         <v>69000</v>
@@ -1113,39 +1114,39 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>61406</v>
+        <v>59067</v>
       </c>
       <c r="F8">
         <v>69000</v>
       </c>
       <c r="G8">
-        <v>11000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>7</v>
+      <c r="A9" s="1">
+        <v>46258</v>
       </c>
       <c r="B9">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E9">
-        <v>151000</v>
+        <v>145036</v>
       </c>
       <c r="F9">
         <v>69000</v>
@@ -1155,20 +1156,20 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>7</v>
+      <c r="A10" s="1">
+        <v>46258</v>
       </c>
       <c r="B10">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E10">
-        <v>59067</v>
+        <v>61406</v>
       </c>
       <c r="F10">
         <v>69000</v>
@@ -1178,26 +1179,26 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>46258</v>
+      <c r="A11" t="s">
+        <v>7</v>
       </c>
       <c r="B11">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>145036</v>
+        <v>151000</v>
       </c>
       <c r="F11">
         <v>69000</v>
       </c>
       <c r="G11">
-        <v>11000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1205,62 +1206,62 @@
         <v>7</v>
       </c>
       <c r="B12">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>145036</v>
+        <v>59067</v>
       </c>
       <c r="F12">
         <v>69000</v>
       </c>
       <c r="G12">
-        <v>11000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>46258</v>
+      <c r="A13" t="s">
+        <v>7</v>
       </c>
       <c r="B13">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>61406</v>
+        <v>153500</v>
       </c>
       <c r="F13">
         <v>69000</v>
       </c>
       <c r="G13">
-        <v>1000</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>7</v>
+      <c r="A14" s="1">
+        <v>46259</v>
       </c>
       <c r="B14">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E14">
-        <v>61406</v>
+        <v>101759</v>
       </c>
       <c r="F14">
         <v>69000</v>
@@ -1274,22 +1275,22 @@
         <v>7</v>
       </c>
       <c r="B15">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>151000</v>
+        <v>102928</v>
       </c>
       <c r="F15">
         <v>69000</v>
       </c>
       <c r="G15">
-        <v>21000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1297,22 +1298,22 @@
         <v>7</v>
       </c>
       <c r="B16">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>59067</v>
+        <v>184553</v>
       </c>
       <c r="F16">
         <v>69000</v>
       </c>
       <c r="G16">
-        <v>1000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1320,39 +1321,39 @@
         <v>7</v>
       </c>
       <c r="B17">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>153500</v>
+        <v>54973</v>
       </c>
       <c r="F17">
         <v>69000</v>
       </c>
       <c r="G17">
-        <v>99000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>46259</v>
+      <c r="A18" t="s">
+        <v>7</v>
       </c>
       <c r="B18">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>101759</v>
+        <v>73327</v>
       </c>
       <c r="F18">
         <v>69000</v>
@@ -1366,22 +1367,22 @@
         <v>7</v>
       </c>
       <c r="B19">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>101759</v>
+        <v>49125</v>
       </c>
       <c r="F19">
         <v>69000</v>
       </c>
       <c r="G19">
-        <v>1000</v>
+        <v>74000</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1389,16 +1390,16 @@
         <v>7</v>
       </c>
       <c r="B20">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>102928</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>69000</v>
@@ -1412,45 +1413,45 @@
         <v>7</v>
       </c>
       <c r="B21">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>184553</v>
+        <v>51464</v>
       </c>
       <c r="F21">
         <v>69000</v>
       </c>
       <c r="G21">
-        <v>100000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>7</v>
+      <c r="A22" s="1">
+        <v>46258</v>
       </c>
       <c r="B22">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E22">
-        <v>54973</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>69000</v>
       </c>
       <c r="G22">
-        <v>1000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1458,16 +1459,16 @@
         <v>7</v>
       </c>
       <c r="B23">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>73327</v>
+        <v>65500</v>
       </c>
       <c r="F23">
         <v>69000</v>
@@ -1481,22 +1482,22 @@
         <v>7</v>
       </c>
       <c r="B24">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>49125</v>
+        <v>53803</v>
       </c>
       <c r="F24">
         <v>69000</v>
       </c>
       <c r="G24">
-        <v>74000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1504,16 +1505,16 @@
         <v>7</v>
       </c>
       <c r="B25">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>199000</v>
       </c>
       <c r="F25">
         <v>69000</v>
@@ -1527,59 +1528,59 @@
         <v>7</v>
       </c>
       <c r="B26">
-        <v>1020</v>
+        <v>1025</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
+        <v>49125</v>
+      </c>
+      <c r="F26">
+        <v>69000</v>
+      </c>
+      <c r="G26">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27">
+        <v>1026</v>
+      </c>
+      <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
         <v>51464</v>
       </c>
-      <c r="F26">
-        <v>69000</v>
-      </c>
-      <c r="G26">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <v>46258</v>
-      </c>
-      <c r="B27">
-        <v>1021</v>
-      </c>
-      <c r="C27" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27">
-        <v>1000</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
       <c r="F27">
         <v>69000</v>
       </c>
       <c r="G27">
-        <v>39000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>7</v>
+      <c r="A28" s="1">
+        <v>46259</v>
       </c>
       <c r="B28">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1588,7 +1589,7 @@
         <v>69000</v>
       </c>
       <c r="G28">
-        <v>39000</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1596,22 +1597,22 @@
         <v>7</v>
       </c>
       <c r="B29">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>65500</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <v>69000</v>
       </c>
       <c r="G29">
-        <v>1000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1619,182 +1620,21 @@
         <v>7</v>
       </c>
       <c r="B30">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>53803</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <v>69000</v>
       </c>
       <c r="G30">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31">
-        <v>1024</v>
-      </c>
-      <c r="C31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <v>199000</v>
-      </c>
-      <c r="F31">
-        <v>69000</v>
-      </c>
-      <c r="G31">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32">
-        <v>1025</v>
-      </c>
-      <c r="C32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32">
-        <v>49125</v>
-      </c>
-      <c r="F32">
-        <v>69000</v>
-      </c>
-      <c r="G32">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33">
-        <v>1026</v>
-      </c>
-      <c r="C33" t="s">
-        <v>33</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33">
-        <v>51464</v>
-      </c>
-      <c r="F33">
-        <v>69000</v>
-      </c>
-      <c r="G33">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
-        <v>46259</v>
-      </c>
-      <c r="B34">
-        <v>1027</v>
-      </c>
-      <c r="C34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D34">
-        <v>1000</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>69000</v>
-      </c>
-      <c r="G34">
-        <v>41000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35">
-        <v>1027</v>
-      </c>
-      <c r="C35" t="s">
-        <v>34</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>69000</v>
-      </c>
-      <c r="G35">
-        <v>41000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36">
-        <v>1028</v>
-      </c>
-      <c r="C36" t="s">
-        <v>35</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>69000</v>
-      </c>
-      <c r="G36">
-        <v>14000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37">
-        <v>1029</v>
-      </c>
-      <c r="C37" t="s">
-        <v>36</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <v>69000</v>
-      </c>
-      <c r="G37">
         <v>0</v>
       </c>
     </row>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="37">
   <si>
     <t>business_date</t>
   </si>
@@ -943,6 +943,7 @@
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
@@ -995,8 +996,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
+      <c r="A3" s="1">
+        <v>46260</v>
       </c>
       <c r="B3">
         <v>1002</v>
@@ -1005,7 +1006,7 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E3">
         <v>151000</v>
@@ -1060,7 +1061,7 @@
         <v>69000</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1087,8 +1088,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>7</v>
+      <c r="A7" s="1">
+        <v>46260</v>
       </c>
       <c r="B7">
         <v>1006</v>
@@ -1097,7 +1098,7 @@
         <v>13</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E7">
         <v>151000</v>
@@ -1363,8 +1364,8 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>7</v>
+      <c r="A19" s="1">
+        <v>46260</v>
       </c>
       <c r="B19">
         <v>1018</v>
@@ -1373,7 +1374,7 @@
         <v>25</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E19">
         <v>49125</v>
@@ -1386,8 +1387,8 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>7</v>
+      <c r="A20" s="1">
+        <v>46260</v>
       </c>
       <c r="B20">
         <v>1019</v>
@@ -1396,7 +1397,7 @@
         <v>26</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E20">
         <v>0</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
   <si>
     <t>business_date</t>
   </si>
@@ -42,25 +42,25 @@
     <t>EGSA2027_Half_Year_achievement</t>
   </si>
   <si>
+    <t>Geetu Bekela</t>
+  </si>
+  <si>
+    <t>Walfana Megersa</t>
+  </si>
+  <si>
+    <t>Fayisa Badhu</t>
+  </si>
+  <si>
+    <t>Silash Dabesa</t>
+  </si>
+  <si>
+    <t>Warkitu Dilba</t>
+  </si>
+  <si>
+    <t>Kenanisa Bikila</t>
+  </si>
+  <si>
     <t>NULL</t>
-  </si>
-  <si>
-    <t>Geetu Bekela</t>
-  </si>
-  <si>
-    <t>Walfana Megersa</t>
-  </si>
-  <si>
-    <t>Fayisa Badhu</t>
-  </si>
-  <si>
-    <t>Silash Dabesa</t>
-  </si>
-  <si>
-    <t>Warkitu Dilba</t>
-  </si>
-  <si>
-    <t>Kenanisa Bikila</t>
   </si>
   <si>
     <t>Lalise Megersa</t>
@@ -941,11 +941,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -973,17 +968,17 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>7</v>
+      <c r="A2" s="1">
+        <v>46261</v>
       </c>
       <c r="B2">
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E2">
         <v>88893</v>
@@ -1003,7 +998,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>1000</v>
@@ -1019,17 +1014,17 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>7</v>
+      <c r="A4" s="1">
+        <v>46261</v>
       </c>
       <c r="B4">
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E4">
         <v>151000</v>
@@ -1049,7 +1044,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>1000</v>
@@ -1072,7 +1067,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6">
         <v>1000</v>
@@ -1095,7 +1090,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7">
         <v>1000</v>
@@ -1112,7 +1107,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>1007</v>
@@ -1180,8 +1175,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>7</v>
+      <c r="A11" s="1">
+        <v>46261</v>
       </c>
       <c r="B11">
         <v>1010</v>
@@ -1190,7 +1185,7 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E11">
         <v>151000</v>
@@ -1204,7 +1199,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>1011</v>
@@ -1226,8 +1221,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>7</v>
+      <c r="A13" s="1">
+        <v>46261</v>
       </c>
       <c r="B13">
         <v>1012</v>
@@ -1236,7 +1231,7 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E13">
         <v>153500</v>
@@ -1273,7 +1268,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B15">
         <v>1014</v>
@@ -1296,7 +1291,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B16">
         <v>1015</v>
@@ -1319,7 +1314,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B17">
         <v>1016</v>
@@ -1342,7 +1337,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>1017</v>
@@ -1411,7 +1406,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B21">
         <v>1020</v>
@@ -1457,7 +1452,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B23">
         <v>1022</v>
@@ -1480,7 +1475,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B24">
         <v>1023</v>
@@ -1503,7 +1498,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B25">
         <v>1024</v>
@@ -1526,7 +1521,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B26">
         <v>1025</v>
@@ -1549,7 +1544,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B27">
         <v>1026</v>
@@ -1595,7 +1590,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B29">
         <v>1028</v>
@@ -1618,7 +1613,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B30">
         <v>1029</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
   <si>
     <t>business_date</t>
   </si>
@@ -941,6 +941,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1589,8 +1591,8 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>13</v>
+      <c r="A29" s="1">
+        <v>46261</v>
       </c>
       <c r="B29">
         <v>1028</v>
@@ -1599,7 +1601,7 @@
         <v>35</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E29">
         <v>0</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>business_date</t>
   </si>
@@ -60,19 +60,19 @@
     <t>Kenanisa Bikila</t>
   </si>
   <si>
+    <t>Lalise Megersa</t>
+  </si>
+  <si>
+    <t>Lami Diro</t>
+  </si>
+  <si>
+    <t>Boki Bayena</t>
+  </si>
+  <si>
+    <t>Salamon Zarihun</t>
+  </si>
+  <si>
     <t>NULL</t>
-  </si>
-  <si>
-    <t>Lalise Megersa</t>
-  </si>
-  <si>
-    <t>Lami Diro</t>
-  </si>
-  <si>
-    <t>Boki Bayena</t>
-  </si>
-  <si>
-    <t>Salamon Zarihun</t>
   </si>
   <si>
     <t>Warki Lemma</t>
@@ -941,9 +941,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1108,17 +1106,17 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>13</v>
+      <c r="A8" s="1">
+        <v>46262</v>
       </c>
       <c r="B8">
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E8">
         <v>59067</v>
@@ -1138,7 +1136,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9">
         <v>1000</v>
@@ -1161,7 +1159,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>1000</v>
@@ -1184,7 +1182,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D11">
         <v>1000</v>
@@ -1201,7 +1199,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>1011</v>
@@ -1270,7 +1268,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>1014</v>
@@ -1293,7 +1291,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>1015</v>
@@ -1316,7 +1314,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>1016</v>
@@ -1338,8 +1336,8 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>13</v>
+      <c r="A18" s="1">
+        <v>46262</v>
       </c>
       <c r="B18">
         <v>1017</v>
@@ -1348,7 +1346,7 @@
         <v>24</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E18">
         <v>73327</v>
@@ -1408,7 +1406,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B21">
         <v>1020</v>
@@ -1454,7 +1452,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B23">
         <v>1022</v>
@@ -1477,7 +1475,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>1023</v>
@@ -1500,7 +1498,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B25">
         <v>1024</v>
@@ -1523,7 +1521,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B26">
         <v>1025</v>
@@ -1546,7 +1544,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B27">
         <v>1026</v>
@@ -1615,7 +1613,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B30">
         <v>1029</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
   <si>
     <t>business_date</t>
   </si>
@@ -72,16 +72,16 @@
     <t>Salamon Zarihun</t>
   </si>
   <si>
+    <t>Warki Lemma</t>
+  </si>
+  <si>
+    <t>Dajane Guta</t>
+  </si>
+  <si>
+    <t>Jabeessaa Dhugumaa</t>
+  </si>
+  <si>
     <t>NULL</t>
-  </si>
-  <si>
-    <t>Warki Lemma</t>
-  </si>
-  <si>
-    <t>Dajane Guta</t>
-  </si>
-  <si>
-    <t>Jabeessaa Dhugumaa</t>
   </si>
   <si>
     <t>Barsisa Merga</t>
@@ -941,7 +941,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1198,17 +1199,17 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>17</v>
+      <c r="A12" s="1">
+        <v>46262</v>
       </c>
       <c r="B12">
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E12">
         <v>59067</v>
@@ -1228,7 +1229,7 @@
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13">
         <v>1000</v>
@@ -1251,7 +1252,7 @@
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14">
         <v>1000</v>
@@ -1268,7 +1269,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>1014</v>
@@ -1291,7 +1292,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B16">
         <v>1015</v>
@@ -1314,7 +1315,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B17">
         <v>1016</v>
@@ -1406,7 +1407,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B21">
         <v>1020</v>
@@ -1451,8 +1452,8 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>17</v>
+      <c r="A23" s="1">
+        <v>46262</v>
       </c>
       <c r="B23">
         <v>1022</v>
@@ -1461,7 +1462,7 @@
         <v>29</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E23">
         <v>65500</v>
@@ -1475,7 +1476,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B24">
         <v>1023</v>
@@ -1498,7 +1499,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B25">
         <v>1024</v>
@@ -1521,7 +1522,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B26">
         <v>1025</v>
@@ -1544,7 +1545,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B27">
         <v>1026</v>
@@ -1613,7 +1614,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B30">
         <v>1029</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
   <si>
     <t>business_date</t>
   </si>
@@ -941,8 +941,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1544,8 +1542,8 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>20</v>
+      <c r="A27" s="1">
+        <v>46263</v>
       </c>
       <c r="B27">
         <v>1026</v>
@@ -1554,7 +1552,7 @@
         <v>33</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E27">
         <v>51464</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t>business_date</t>
   </si>
@@ -1289,8 +1289,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>20</v>
+      <c r="A16" s="1">
+        <v>46263</v>
       </c>
       <c r="B16">
         <v>1015</v>
@@ -1299,7 +1299,7 @@
         <v>22</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E16">
         <v>184553</v>
@@ -1308,7 +1308,7 @@
         <v>69000</v>
       </c>
       <c r="G16">
-        <v>100000</v>
+        <v>101000</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1473,8 +1473,8 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>20</v>
+      <c r="A24" s="1">
+        <v>46263</v>
       </c>
       <c r="B24">
         <v>1023</v>
@@ -1483,7 +1483,7 @@
         <v>30</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E24">
         <v>53803</v>
@@ -1519,8 +1519,8 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>20</v>
+      <c r="A26" s="1">
+        <v>46263</v>
       </c>
       <c r="B26">
         <v>1025</v>
@@ -1529,7 +1529,7 @@
         <v>32</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E26">
         <v>49125</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>business_date</t>
   </si>
@@ -941,6 +941,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1404,8 +1405,8 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>20</v>
+      <c r="A21" s="1">
+        <v>46264</v>
       </c>
       <c r="B21">
         <v>1020</v>
@@ -1414,7 +1415,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E21">
         <v>51464</v>
@@ -1611,8 +1612,8 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>20</v>
+      <c r="A30" s="1">
+        <v>46265</v>
       </c>
       <c r="B30">
         <v>1029</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -941,7 +941,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -1621,7 +1621,7 @@
         <v>36</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E30">
         <v>0</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
     <t>business_date</t>
   </si>
@@ -81,13 +81,13 @@
     <t>Jabeessaa Dhugumaa</t>
   </si>
   <si>
+    <t>Barsisa Merga</t>
+  </si>
+  <si>
+    <t>Abera Asefa</t>
+  </si>
+  <si>
     <t>NULL</t>
-  </si>
-  <si>
-    <t>Barsisa Merga</t>
-  </si>
-  <si>
-    <t>Abera Asefa</t>
   </si>
   <si>
     <t>Alamuu Guutaa</t>
@@ -1266,17 +1266,17 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>20</v>
+      <c r="A15" s="1">
+        <v>46265</v>
       </c>
       <c r="B15">
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E15">
         <v>102928</v>
@@ -1296,7 +1296,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16">
         <v>1000</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B17">
         <v>1016</v>
@@ -1497,7 +1497,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B25">
         <v>1024</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20724" windowHeight="3192"/>
   </bookViews>
   <sheets>
     <sheet name="EGSA2026_27_Monthly_report" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>business_date</t>
   </si>
@@ -87,31 +87,31 @@
     <t>Abera Asefa</t>
   </si>
   <si>
+    <t>Alamuu Guutaa</t>
+  </si>
+  <si>
+    <t>Naggasaa Dheeressaa</t>
+  </si>
+  <si>
+    <t>Jaalataa magarsaa</t>
+  </si>
+  <si>
+    <t>Bedasa Geleta</t>
+  </si>
+  <si>
+    <t>Chaluma Uma</t>
+  </si>
+  <si>
+    <t>Mamo Tesfaye</t>
+  </si>
+  <si>
+    <t>Worku Bekele</t>
+  </si>
+  <si>
+    <t>Milkesa Gebre</t>
+  </si>
+  <si>
     <t>NULL</t>
-  </si>
-  <si>
-    <t>Alamuu Guutaa</t>
-  </si>
-  <si>
-    <t>Naggasaa Dheeressaa</t>
-  </si>
-  <si>
-    <t>Jaalataa magarsaa</t>
-  </si>
-  <si>
-    <t>Bedasa Geleta</t>
-  </si>
-  <si>
-    <t>Chaluma Uma</t>
-  </si>
-  <si>
-    <t>Mamo Tesfaye</t>
-  </si>
-  <si>
-    <t>Worku Bekele</t>
-  </si>
-  <si>
-    <t>Milkesa Gebre</t>
   </si>
   <si>
     <t>Worku Guta</t>
@@ -1312,17 +1312,17 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>22</v>
+      <c r="A17" s="1">
+        <v>46265</v>
       </c>
       <c r="B17">
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E17">
         <v>54973</v>
@@ -1331,7 +1331,7 @@
         <v>69000</v>
       </c>
       <c r="G17">
-        <v>1000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1342,7 +1342,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D18">
         <v>1000</v>
@@ -1365,7 +1365,7 @@
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19">
         <v>1000</v>
@@ -1388,7 +1388,7 @@
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20">
         <v>1000</v>
@@ -1411,7 +1411,7 @@
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D21">
         <v>1000</v>
@@ -1434,7 +1434,7 @@
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D22">
         <v>1000</v>
@@ -1446,7 +1446,7 @@
         <v>69000</v>
       </c>
       <c r="G22">
-        <v>39000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1457,7 +1457,7 @@
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>1000</v>
@@ -1480,7 +1480,7 @@
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24">
         <v>1000</v>
@@ -1497,7 +1497,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B25">
         <v>1024</v>
@@ -1621,7 +1621,7 @@
         <v>36</v>
       </c>
       <c r="D30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>0</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20724" windowHeight="3192"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
   </bookViews>
   <sheets>
     <sheet name="EGSA2026_27_Monthly_report" sheetId="1" r:id="rId1"/>
@@ -1446,7 +1446,7 @@
         <v>69000</v>
       </c>
       <c r="G22">
-        <v>50000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1607,7 +1607,7 @@
         <v>69000</v>
       </c>
       <c r="G29">
-        <v>14000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1621,7 +1621,7 @@
         <v>36</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E30">
         <v>0</v>
